--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-14T11:37:57+00:00</t>
+    <t>2024-10-14T15:26:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-14T15:26:29+00:00</t>
+    <t>2024-10-15T04:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T04:28:43+00:00</t>
+    <t>2024-10-15T09:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T09:44:23+00:00</t>
+    <t>2024-10-15T10:29:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T10:29:21+00:00</t>
+    <t>2024-10-15T15:26:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T15:26:25+00:00</t>
+    <t>2024-10-16T04:28:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T04:28:57+00:00</t>
+    <t>2024-10-16T10:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T10:25:25+00:00</t>
+    <t>2024-10-16T12:37:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T12:37:09+00:00</t>
+    <t>2024-10-17T04:29:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T04:29:22+00:00</t>
+    <t>2024-10-17T10:28:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T10:28:31+00:00</t>
+    <t>2024-10-17T15:25:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T15:25:42+00:00</t>
+    <t>2024-10-18T04:29:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T04:29:52+00:00</t>
+    <t>2024-10-18T07:07:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T07:07:45+00:00</t>
+    <t>2024-10-18T10:29:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T10:29:00+00:00</t>
+    <t>2024-10-18T15:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T15:28:09+00:00</t>
+    <t>2024-10-19T04:28:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-19T04:28:49+00:00</t>
+    <t>2024-10-19T10:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-19T10:25:11+00:00</t>
+    <t>2024-10-19T15:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-19T15:24:42+00:00</t>
+    <t>2024-10-20T04:28:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T04:28:58+00:00</t>
+    <t>2024-10-20T10:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T10:26:58+00:00</t>
+    <t>2024-10-20T15:25:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T15:25:43+00:00</t>
+    <t>2024-10-21T04:29:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-21T04:29:35+00:00</t>
+    <t>2024-10-21T10:29:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-21T10:29:31+00:00</t>
+    <t>2024-10-21T15:27:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
